--- a/InputData/elec/BGDPbES/BAU Guaranteed Dispatch Perc by Elec Source.xlsx
+++ b/InputData/elec/BGDPbES/BAU Guaranteed Dispatch Perc by Elec Source.xlsx
@@ -1,21 +1,21 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="26731"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="26924"/>
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Olivia Ashmoore\Documents\EPS_Models by Region\RMI\RMI_all_states\IA\elec\BGDPbES\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E097A784-DAEE-4B01-8200-88FB23ABCAC9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{1AB1CD2F-3030-48E6-A470-41615333E3EF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="1170" yWindow="1170" windowWidth="21600" windowHeight="12645" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="13395" yWindow="345" windowWidth="15360" windowHeight="16755" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="About" sheetId="1" r:id="rId1"/>
-    <sheet name="Wgtd Avg Expected Cap Factors" sheetId="2" r:id="rId2"/>
-    <sheet name="BGDPbES" sheetId="3" r:id="rId3"/>
+    <sheet name="Wgtd Avg Expected Cap Factors" sheetId="8" r:id="rId2"/>
+    <sheet name="BGDPbES" sheetId="2" r:id="rId3"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -26,8 +26,6 @@
         <xcalcf:feature name="microsoft.com:FV"/>
         <xcalcf:feature name="microsoft.com:CNMTM"/>
         <xcalcf:feature name="microsoft.com:LET_WF"/>
-        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
-        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
       </xcalcf:calcFeatures>
     </ext>
   </extLst>
@@ -37,187 +35,187 @@
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
 <sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="61" uniqueCount="61">
   <si>
+    <t>Notes:</t>
+  </si>
+  <si>
+    <t>nuclear</t>
+  </si>
+  <si>
+    <t>hydro</t>
+  </si>
+  <si>
+    <t>solar PV</t>
+  </si>
+  <si>
+    <t>solar thermal</t>
+  </si>
+  <si>
+    <t>biomass</t>
+  </si>
+  <si>
+    <t>This variable is used to specify the percentage of potential electricity output from each</t>
+  </si>
+  <si>
+    <t>geothermal</t>
+  </si>
+  <si>
+    <t>petroleum</t>
+  </si>
+  <si>
+    <t>natural gas peaker</t>
+  </si>
+  <si>
     <t>BGDPbES BAU Guaranteed Dispatch Percentage by Electricity Source</t>
   </si>
   <si>
+    <t>source that is guaranteed (e.g. dispatched before any least-cost dispatching</t>
+  </si>
+  <si>
+    <t>begins) in the BAU case.</t>
+  </si>
+  <si>
+    <t>lignite</t>
+  </si>
+  <si>
+    <t>hard coal</t>
+  </si>
+  <si>
+    <t>onshore wind</t>
+  </si>
+  <si>
+    <t>offshore wind</t>
+  </si>
+  <si>
+    <t>crude oil</t>
+  </si>
+  <si>
+    <t>heavy or residual fuel oil</t>
+  </si>
+  <si>
+    <t>municipal solid waste</t>
+  </si>
+  <si>
+    <t>BAU Guaranteed Dispatch (dimensionless)</t>
+  </si>
+  <si>
+    <t>Source:</t>
+  </si>
+  <si>
+    <t>natural gas steam turbine</t>
+  </si>
+  <si>
+    <t>natural gas combined cycle</t>
+  </si>
+  <si>
+    <t>Time (Year)</t>
+  </si>
+  <si>
+    <t>Weighted Average Expected Capacity Factors[hard coal es] : MostRecentRun</t>
+  </si>
+  <si>
+    <t>Weighted Average Expected Capacity Factors[natural gas steam turbine es] : MostRecentRun</t>
+  </si>
+  <si>
+    <t>Weighted Average Expected Capacity Factors[natural gas combined cycle es] : MostRecentRun</t>
+  </si>
+  <si>
+    <t>Weighted Average Expected Capacity Factors[nuclear es] : MostRecentRun</t>
+  </si>
+  <si>
+    <t>Weighted Average Expected Capacity Factors[hydro es] : MostRecentRun</t>
+  </si>
+  <si>
+    <t>Weighted Average Expected Capacity Factors[onshore wind es] : MostRecentRun</t>
+  </si>
+  <si>
+    <t>Weighted Average Expected Capacity Factors[solar PV es] : MostRecentRun</t>
+  </si>
+  <si>
+    <t>Weighted Average Expected Capacity Factors[solar thermal es] : MostRecentRun</t>
+  </si>
+  <si>
+    <t>Weighted Average Expected Capacity Factors[biomass es] : MostRecentRun</t>
+  </si>
+  <si>
+    <t>Weighted Average Expected Capacity Factors[geothermal es] : MostRecentRun</t>
+  </si>
+  <si>
+    <t>Weighted Average Expected Capacity Factors[petroleum es] : MostRecentRun</t>
+  </si>
+  <si>
+    <t>Weighted Average Expected Capacity Factors[natural gas peaker es] : MostRecentRun</t>
+  </si>
+  <si>
+    <t>Weighted Average Expected Capacity Factors[lignite es] : MostRecentRun</t>
+  </si>
+  <si>
+    <t>Weighted Average Expected Capacity Factors[offshore wind es] : MostRecentRun</t>
+  </si>
+  <si>
+    <t>Weighted Average Expected Capacity Factors[crude oil es] : MostRecentRun</t>
+  </si>
+  <si>
+    <t>Weighted Average Expected Capacity Factors[heavy or residual fuel oil es] : MostRecentRun</t>
+  </si>
+  <si>
+    <t>Weighted Average Expected Capacity Factors[municipal solid waste es] : MostRecentRun</t>
+  </si>
+  <si>
+    <t>Petroleum</t>
+  </si>
+  <si>
+    <t>Weighted Average Expected Capacity Factors (calculated EPS variable)</t>
+  </si>
+  <si>
+    <t>For nuclear plants, we guarantee full dispatch, as regulators and utilities often run</t>
+  </si>
+  <si>
+    <t>these plants as baseload irresective of cost, rather than ramping them up and down.</t>
+  </si>
+  <si>
+    <t>For petroleum, we use the weighted average expected capacity factor.</t>
+  </si>
+  <si>
+    <t>In reality, petroleum is primarily used in fuel-switching applications in New England</t>
+  </si>
+  <si>
+    <t>(where there can be specific, unusual hours of NG shortage due to pipeline congestion)</t>
+  </si>
+  <si>
+    <t>and in places like Hawaii, without much NG access, where it is easier to transport petroleum</t>
+  </si>
+  <si>
+    <t>by ship due to its higher volumetric energy density.</t>
+  </si>
+  <si>
+    <t>We can't capture some of these unusual hours and sub-regional dynamics directly, so</t>
+  </si>
+  <si>
+    <t>we use guaranteed dispatch to align modeled petroleum dispatch with real-world experience.</t>
+  </si>
+  <si>
+    <t>hard coal w CCS</t>
+  </si>
+  <si>
+    <t>natural gas combined cycle w CCS</t>
+  </si>
+  <si>
+    <t>biomass w CCS</t>
+  </si>
+  <si>
+    <t>lignite w CCS</t>
+  </si>
+  <si>
+    <t>small modular reactor</t>
+  </si>
+  <si>
+    <t>hydrogen combustion turbine</t>
+  </si>
+  <si>
+    <t>hydrogen combined cycle</t>
+  </si>
+  <si>
     <t>Iowa</t>
-  </si>
-  <si>
-    <t>Source:</t>
-  </si>
-  <si>
-    <t>Petroleum</t>
-  </si>
-  <si>
-    <t>Weighted Average Expected Capacity Factors (calculated EPS variable)</t>
-  </si>
-  <si>
-    <t>Notes:</t>
-  </si>
-  <si>
-    <t>This variable is used to specify the percentage of potential electricity output from each</t>
-  </si>
-  <si>
-    <t>source that is guaranteed (e.g. dispatched before any least-cost dispatching</t>
-  </si>
-  <si>
-    <t>begins) in the BAU case.</t>
-  </si>
-  <si>
-    <t>For nuclear plants, we guarantee full dispatch, as regulators and utilities often run</t>
-  </si>
-  <si>
-    <t>these plants as baseload irresective of cost, rather than ramping them up and down.</t>
-  </si>
-  <si>
-    <t>For petroleum, we use the weighted average expected capacity factor.</t>
-  </si>
-  <si>
-    <t>In reality, petroleum is primarily used in fuel-switching applications in New England</t>
-  </si>
-  <si>
-    <t>(where there can be specific, unusual hours of NG shortage due to pipeline congestion)</t>
-  </si>
-  <si>
-    <t>and in places like Hawaii, without much NG access, where it is easier to transport petroleum</t>
-  </si>
-  <si>
-    <t>by ship due to its higher volumetric energy density.</t>
-  </si>
-  <si>
-    <t>We can't capture some of these unusual hours and sub-regional dynamics directly, so</t>
-  </si>
-  <si>
-    <t>we use guaranteed dispatch to align modeled petroleum dispatch with real-world experience.</t>
-  </si>
-  <si>
-    <t>Time (Year)</t>
-  </si>
-  <si>
-    <t>Weighted Average Expected Capacity Factors[hard coal es] : MostRecentRun</t>
-  </si>
-  <si>
-    <t>Weighted Average Expected Capacity Factors[natural gas steam turbine es] : MostRecentRun</t>
-  </si>
-  <si>
-    <t>Weighted Average Expected Capacity Factors[natural gas combined cycle es] : MostRecentRun</t>
-  </si>
-  <si>
-    <t>Weighted Average Expected Capacity Factors[nuclear es] : MostRecentRun</t>
-  </si>
-  <si>
-    <t>Weighted Average Expected Capacity Factors[hydro es] : MostRecentRun</t>
-  </si>
-  <si>
-    <t>Weighted Average Expected Capacity Factors[onshore wind es] : MostRecentRun</t>
-  </si>
-  <si>
-    <t>Weighted Average Expected Capacity Factors[solar PV es] : MostRecentRun</t>
-  </si>
-  <si>
-    <t>Weighted Average Expected Capacity Factors[solar thermal es] : MostRecentRun</t>
-  </si>
-  <si>
-    <t>Weighted Average Expected Capacity Factors[biomass es] : MostRecentRun</t>
-  </si>
-  <si>
-    <t>Weighted Average Expected Capacity Factors[geothermal es] : MostRecentRun</t>
-  </si>
-  <si>
-    <t>Weighted Average Expected Capacity Factors[petroleum es] : MostRecentRun</t>
-  </si>
-  <si>
-    <t>Weighted Average Expected Capacity Factors[natural gas peaker es] : MostRecentRun</t>
-  </si>
-  <si>
-    <t>Weighted Average Expected Capacity Factors[lignite es] : MostRecentRun</t>
-  </si>
-  <si>
-    <t>Weighted Average Expected Capacity Factors[offshore wind es] : MostRecentRun</t>
-  </si>
-  <si>
-    <t>Weighted Average Expected Capacity Factors[crude oil es] : MostRecentRun</t>
-  </si>
-  <si>
-    <t>Weighted Average Expected Capacity Factors[heavy or residual fuel oil es] : MostRecentRun</t>
-  </si>
-  <si>
-    <t>Weighted Average Expected Capacity Factors[municipal solid waste es] : MostRecentRun</t>
-  </si>
-  <si>
-    <t>BAU Guaranteed Dispatch (dimensionless)</t>
-  </si>
-  <si>
-    <t>hard coal</t>
-  </si>
-  <si>
-    <t>natural gas steam turbine</t>
-  </si>
-  <si>
-    <t>natural gas combined cycle</t>
-  </si>
-  <si>
-    <t>nuclear</t>
-  </si>
-  <si>
-    <t>hydro</t>
-  </si>
-  <si>
-    <t>onshore wind</t>
-  </si>
-  <si>
-    <t>solar PV</t>
-  </si>
-  <si>
-    <t>solar thermal</t>
-  </si>
-  <si>
-    <t>biomass</t>
-  </si>
-  <si>
-    <t>geothermal</t>
-  </si>
-  <si>
-    <t>petroleum</t>
-  </si>
-  <si>
-    <t>natural gas peaker</t>
-  </si>
-  <si>
-    <t>lignite</t>
-  </si>
-  <si>
-    <t>offshore wind</t>
-  </si>
-  <si>
-    <t>crude oil</t>
-  </si>
-  <si>
-    <t>heavy or residual fuel oil</t>
-  </si>
-  <si>
-    <t>municipal solid waste</t>
-  </si>
-  <si>
-    <t>hard coal w CCS</t>
-  </si>
-  <si>
-    <t>natural gas combined cycle w CCS</t>
-  </si>
-  <si>
-    <t>biomass w CCS</t>
-  </si>
-  <si>
-    <t>lignite w CCS</t>
-  </si>
-  <si>
-    <t>small modular reactor</t>
-  </si>
-  <si>
-    <t>hydrogen combustion turbine</t>
-  </si>
-  <si>
-    <t>hydrogen combined cycle</t>
   </si>
 </sst>
 </file>
@@ -282,7 +280,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="7">
+  <cellXfs count="8">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
@@ -298,6 +296,7 @@
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -602,106 +601,109 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:B23"/>
+  <dimension ref="A1:C23"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="2" max="2" width="24.5703125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="B1" t="s">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="3" spans="1:2" x14ac:dyDescent="0.25">
+        <v>60</v>
+      </c>
+      <c r="C1" s="7">
+        <v>45236</v>
+      </c>
+    </row>
+    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A3" s="1" t="s">
-        <v>2</v>
+        <v>21</v>
       </c>
       <c r="B3" s="4" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="4" spans="1:2" x14ac:dyDescent="0.25">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="4" spans="1:3" x14ac:dyDescent="0.25">
       <c r="B4" s="5" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="9" spans="1:2" x14ac:dyDescent="0.25">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="9" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A9" s="1" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="10" spans="1:2" x14ac:dyDescent="0.25">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="10" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
         <v>6</v>
       </c>
     </row>
-    <row r="11" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="12" spans="1:2" x14ac:dyDescent="0.25">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="12" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="14" spans="1:2" x14ac:dyDescent="0.25">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="14" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="15" spans="1:2" x14ac:dyDescent="0.25">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="15" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
-        <v>10</v>
+        <v>45</v>
       </c>
     </row>
     <row r="17" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
-        <v>11</v>
+        <v>46</v>
       </c>
     </row>
     <row r="18" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
-        <v>12</v>
+        <v>47</v>
       </c>
     </row>
     <row r="19" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
-        <v>13</v>
+        <v>48</v>
       </c>
     </row>
     <row r="20" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
-        <v>14</v>
+        <v>49</v>
       </c>
     </row>
     <row r="21" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
-        <v>15</v>
+        <v>50</v>
       </c>
     </row>
     <row r="22" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
-        <v>16</v>
+        <v>51</v>
       </c>
     </row>
     <row r="23" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
-        <v>17</v>
+        <v>52</v>
       </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup orientation="portrait" horizontalDpi="1200" verticalDpi="1200"/>
+  <pageSetup orientation="portrait" horizontalDpi="1200" verticalDpi="1200" r:id="rId1"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{AF2722D0-CF31-4EFA-BD71-F29BE900266B}">
   <dimension ref="A1:AF18"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
@@ -710,7 +712,7 @@
   <sheetData>
     <row r="1" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
-        <v>18</v>
+        <v>24</v>
       </c>
       <c r="B1">
         <v>2020</v>
@@ -808,7 +810,7 @@
     </row>
     <row r="2" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>19</v>
+        <v>25</v>
       </c>
       <c r="B2">
         <v>0.54992799999999997</v>
@@ -906,7 +908,7 @@
     </row>
     <row r="3" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>20</v>
+        <v>26</v>
       </c>
       <c r="B3">
         <v>0.133577</v>
@@ -1004,7 +1006,7 @@
     </row>
     <row r="4" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>21</v>
+        <v>27</v>
       </c>
       <c r="B4">
         <v>0.46789599999999998</v>
@@ -1102,7 +1104,7 @@
     </row>
     <row r="5" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>22</v>
+        <v>28</v>
       </c>
       <c r="B5">
         <v>0.91180000000000005</v>
@@ -1200,7 +1202,7 @@
     </row>
     <row r="6" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>23</v>
+        <v>29</v>
       </c>
       <c r="B6">
         <v>0.405389</v>
@@ -1298,7 +1300,7 @@
     </row>
     <row r="7" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>24</v>
+        <v>30</v>
       </c>
       <c r="B7">
         <v>0.38150099999999998</v>
@@ -1396,7 +1398,7 @@
     </row>
     <row r="8" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
-        <v>25</v>
+        <v>31</v>
       </c>
       <c r="B8">
         <v>0.27117599999999997</v>
@@ -1494,7 +1496,7 @@
     </row>
     <row r="9" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
-        <v>26</v>
+        <v>32</v>
       </c>
       <c r="B9">
         <v>0.23492099999999999</v>
@@ -1592,7 +1594,7 @@
     </row>
     <row r="10" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
-        <v>27</v>
+        <v>33</v>
       </c>
       <c r="B10">
         <v>0.67415599999999998</v>
@@ -1690,7 +1692,7 @@
     </row>
     <row r="11" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
-        <v>28</v>
+        <v>34</v>
       </c>
       <c r="B11">
         <v>0.85009900000000005</v>
@@ -1788,7 +1790,7 @@
     </row>
     <row r="12" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
-        <v>29</v>
+        <v>35</v>
       </c>
       <c r="B12">
         <v>5.6003999999999998E-2</v>
@@ -1886,7 +1888,7 @@
     </row>
     <row r="13" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
-        <v>30</v>
+        <v>36</v>
       </c>
       <c r="B13">
         <v>0.12672900000000001</v>
@@ -1984,7 +1986,7 @@
     </row>
     <row r="14" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
-        <v>31</v>
+        <v>37</v>
       </c>
       <c r="B14">
         <v>0.54992799999999997</v>
@@ -2082,7 +2084,7 @@
     </row>
     <row r="15" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
-        <v>32</v>
+        <v>38</v>
       </c>
       <c r="B15">
         <v>0.42069899999999999</v>
@@ -2180,7 +2182,7 @@
     </row>
     <row r="16" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
-        <v>33</v>
+        <v>39</v>
       </c>
       <c r="B16">
         <v>0</v>
@@ -2278,7 +2280,7 @@
     </row>
     <row r="17" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
-        <v>34</v>
+        <v>40</v>
       </c>
       <c r="B17">
         <v>0</v>
@@ -2376,7 +2378,7 @@
     </row>
     <row r="18" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
-        <v>35</v>
+        <v>41</v>
       </c>
       <c r="B18">
         <v>0.67415599999999998</v>
@@ -2478,7 +2480,7 @@
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <sheetPr>
     <tabColor theme="3"/>
   </sheetPr>
@@ -2489,9 +2491,9 @@
     <col min="2" max="2" width="11.28515625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:37" ht="45" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:37" ht="45" x14ac:dyDescent="0.25">
       <c r="A1" s="3" t="s">
-        <v>36</v>
+        <v>20</v>
       </c>
       <c r="B1" s="2">
         <v>2015</v>
@@ -2604,7 +2606,7 @@
     </row>
     <row r="2" spans="1:37" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>37</v>
+        <v>14</v>
       </c>
       <c r="B2">
         <v>0</v>
@@ -2717,7 +2719,7 @@
     </row>
     <row r="3" spans="1:37" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>38</v>
+        <v>22</v>
       </c>
       <c r="B3">
         <v>0</v>
@@ -2744,7 +2746,7 @@
         <v>0</v>
       </c>
       <c r="J3">
-        <f t="shared" ref="J3:S4" si="0">$B3</f>
+        <f t="shared" ref="J3:R4" si="0">$B3</f>
         <v>0</v>
       </c>
       <c r="K3">
@@ -2780,11 +2782,11 @@
         <v>0</v>
       </c>
       <c r="S3">
-        <f t="shared" si="0"/>
+        <f t="shared" ref="J3:AK10" si="1">$B3</f>
         <v>0</v>
       </c>
       <c r="T3">
-        <f t="shared" ref="T3:AC4" si="1">$B3</f>
+        <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="U3">
@@ -2824,41 +2826,41 @@
         <v>0</v>
       </c>
       <c r="AD3">
-        <f t="shared" ref="AD3:AK4" si="2">$B3</f>
+        <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="AE3">
-        <f t="shared" si="2"/>
+        <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="AF3">
-        <f t="shared" si="2"/>
+        <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="AG3">
-        <f t="shared" si="2"/>
+        <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="AH3">
-        <f t="shared" si="2"/>
+        <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="AI3">
-        <f t="shared" si="2"/>
+        <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="AJ3">
-        <f t="shared" si="2"/>
+        <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="AK3">
-        <f t="shared" si="2"/>
+        <f t="shared" si="1"/>
         <v>0</v>
       </c>
     </row>
     <row r="4" spans="1:37" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>39</v>
+        <v>23</v>
       </c>
       <c r="B4">
         <v>0</v>
@@ -2921,7 +2923,7 @@
         <v>0</v>
       </c>
       <c r="S4">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="T4">
@@ -2965,41 +2967,41 @@
         <v>0</v>
       </c>
       <c r="AD4">
-        <f t="shared" si="2"/>
+        <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="AE4">
-        <f t="shared" si="2"/>
+        <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="AF4">
-        <f t="shared" si="2"/>
+        <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="AG4">
-        <f t="shared" si="2"/>
+        <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="AH4">
-        <f t="shared" si="2"/>
+        <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="AI4">
-        <f t="shared" si="2"/>
+        <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="AJ4">
-        <f t="shared" si="2"/>
+        <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="AK4">
-        <f t="shared" si="2"/>
+        <f t="shared" si="1"/>
         <v>0</v>
       </c>
     </row>
     <row r="5" spans="1:37" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>40</v>
+        <v>1</v>
       </c>
       <c r="B5">
         <v>1</v>
@@ -3029,117 +3031,117 @@
         <v>1</v>
       </c>
       <c r="K5">
-        <f t="shared" ref="K5:T10" si="3">$B5</f>
+        <f t="shared" si="1"/>
         <v>1</v>
       </c>
       <c r="L5">
-        <f t="shared" si="3"/>
+        <f t="shared" si="1"/>
         <v>1</v>
       </c>
       <c r="M5">
-        <f t="shared" si="3"/>
+        <f t="shared" si="1"/>
         <v>1</v>
       </c>
       <c r="N5">
-        <f t="shared" si="3"/>
+        <f t="shared" si="1"/>
         <v>1</v>
       </c>
       <c r="O5">
-        <f t="shared" si="3"/>
+        <f t="shared" si="1"/>
         <v>1</v>
       </c>
       <c r="P5">
-        <f t="shared" si="3"/>
+        <f t="shared" si="1"/>
         <v>1</v>
       </c>
       <c r="Q5">
-        <f t="shared" si="3"/>
+        <f t="shared" si="1"/>
         <v>1</v>
       </c>
       <c r="R5">
-        <f t="shared" si="3"/>
+        <f t="shared" si="1"/>
         <v>1</v>
       </c>
       <c r="S5">
-        <f t="shared" si="3"/>
+        <f t="shared" si="1"/>
         <v>1</v>
       </c>
       <c r="T5">
-        <f t="shared" si="3"/>
+        <f t="shared" si="1"/>
         <v>1</v>
       </c>
       <c r="U5">
-        <f t="shared" ref="U5:AD10" si="4">$B5</f>
+        <f t="shared" si="1"/>
         <v>1</v>
       </c>
       <c r="V5">
-        <f t="shared" si="4"/>
+        <f t="shared" si="1"/>
         <v>1</v>
       </c>
       <c r="W5">
-        <f t="shared" si="4"/>
+        <f t="shared" si="1"/>
         <v>1</v>
       </c>
       <c r="X5">
-        <f t="shared" si="4"/>
+        <f t="shared" si="1"/>
         <v>1</v>
       </c>
       <c r="Y5">
-        <f t="shared" si="4"/>
+        <f t="shared" si="1"/>
         <v>1</v>
       </c>
       <c r="Z5">
-        <f t="shared" si="4"/>
+        <f t="shared" si="1"/>
         <v>1</v>
       </c>
       <c r="AA5">
-        <f t="shared" si="4"/>
+        <f t="shared" si="1"/>
         <v>1</v>
       </c>
       <c r="AB5">
-        <f t="shared" si="4"/>
+        <f t="shared" si="1"/>
         <v>1</v>
       </c>
       <c r="AC5">
-        <f t="shared" si="4"/>
+        <f t="shared" si="1"/>
         <v>1</v>
       </c>
       <c r="AD5">
-        <f t="shared" si="4"/>
+        <f t="shared" si="1"/>
         <v>1</v>
       </c>
       <c r="AE5">
-        <f t="shared" ref="AE5:AK10" si="5">$B5</f>
+        <f t="shared" si="1"/>
         <v>1</v>
       </c>
       <c r="AF5">
-        <f t="shared" si="5"/>
+        <f t="shared" si="1"/>
         <v>1</v>
       </c>
       <c r="AG5">
-        <f t="shared" si="5"/>
+        <f t="shared" si="1"/>
         <v>1</v>
       </c>
       <c r="AH5">
-        <f t="shared" si="5"/>
+        <f t="shared" si="1"/>
         <v>1</v>
       </c>
       <c r="AI5">
-        <f t="shared" si="5"/>
+        <f t="shared" si="1"/>
         <v>1</v>
       </c>
       <c r="AJ5">
-        <f t="shared" si="5"/>
+        <f t="shared" si="1"/>
         <v>1</v>
       </c>
       <c r="AK5">
-        <f t="shared" si="5"/>
+        <f t="shared" si="1"/>
         <v>1</v>
       </c>
     </row>
     <row r="6" spans="1:37" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>41</v>
+        <v>2</v>
       </c>
       <c r="B6">
         <v>0</v>
@@ -3166,121 +3168,121 @@
         <v>0</v>
       </c>
       <c r="J6">
-        <f>$B6</f>
+        <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="K6">
-        <f t="shared" si="3"/>
+        <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="L6">
-        <f t="shared" si="3"/>
+        <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="M6">
-        <f t="shared" si="3"/>
+        <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="N6">
-        <f t="shared" si="3"/>
+        <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="O6">
-        <f t="shared" si="3"/>
+        <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="P6">
-        <f t="shared" si="3"/>
+        <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="Q6">
-        <f t="shared" si="3"/>
+        <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="R6">
-        <f t="shared" si="3"/>
+        <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="S6">
-        <f t="shared" si="3"/>
+        <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="T6">
-        <f t="shared" si="3"/>
+        <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="U6">
-        <f t="shared" si="4"/>
+        <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="V6">
-        <f t="shared" si="4"/>
+        <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="W6">
-        <f t="shared" si="4"/>
+        <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="X6">
-        <f t="shared" si="4"/>
+        <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="Y6">
-        <f t="shared" si="4"/>
+        <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="Z6">
-        <f t="shared" si="4"/>
+        <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="AA6">
-        <f t="shared" si="4"/>
+        <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="AB6">
-        <f t="shared" si="4"/>
+        <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="AC6">
-        <f t="shared" si="4"/>
+        <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="AD6">
-        <f t="shared" si="4"/>
+        <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="AE6">
-        <f t="shared" si="5"/>
+        <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="AF6">
-        <f t="shared" si="5"/>
+        <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="AG6">
-        <f t="shared" si="5"/>
+        <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="AH6">
-        <f t="shared" si="5"/>
+        <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="AI6">
-        <f t="shared" si="5"/>
+        <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="AJ6">
-        <f t="shared" si="5"/>
+        <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="AK6">
-        <f t="shared" si="5"/>
+        <f t="shared" si="1"/>
         <v>0</v>
       </c>
     </row>
     <row r="7" spans="1:37" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>42</v>
+        <v>15</v>
       </c>
       <c r="B7">
         <v>0</v>
@@ -3307,121 +3309,121 @@
         <v>0</v>
       </c>
       <c r="J7">
-        <f>$B7</f>
+        <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="K7">
-        <f t="shared" si="3"/>
+        <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="L7">
-        <f t="shared" si="3"/>
+        <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="M7">
-        <f t="shared" si="3"/>
+        <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="N7">
-        <f t="shared" si="3"/>
+        <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="O7">
-        <f t="shared" si="3"/>
+        <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="P7">
-        <f t="shared" si="3"/>
+        <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="Q7">
-        <f t="shared" si="3"/>
+        <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="R7">
-        <f t="shared" si="3"/>
+        <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="S7">
-        <f t="shared" si="3"/>
+        <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="T7">
-        <f t="shared" si="3"/>
+        <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="U7">
-        <f t="shared" si="4"/>
+        <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="V7">
-        <f t="shared" si="4"/>
+        <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="W7">
-        <f t="shared" si="4"/>
+        <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="X7">
-        <f t="shared" si="4"/>
+        <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="Y7">
-        <f t="shared" si="4"/>
+        <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="Z7">
-        <f t="shared" si="4"/>
+        <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="AA7">
-        <f t="shared" si="4"/>
+        <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="AB7">
-        <f t="shared" si="4"/>
+        <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="AC7">
-        <f t="shared" si="4"/>
+        <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="AD7">
-        <f t="shared" si="4"/>
+        <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="AE7">
-        <f t="shared" si="5"/>
+        <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="AF7">
-        <f t="shared" si="5"/>
+        <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="AG7">
-        <f t="shared" si="5"/>
+        <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="AH7">
-        <f t="shared" si="5"/>
+        <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="AI7">
-        <f t="shared" si="5"/>
+        <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="AJ7">
-        <f t="shared" si="5"/>
+        <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="AK7">
-        <f t="shared" si="5"/>
+        <f t="shared" si="1"/>
         <v>0</v>
       </c>
     </row>
     <row r="8" spans="1:37" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
-        <v>43</v>
+        <v>3</v>
       </c>
       <c r="B8">
         <v>0</v>
@@ -3448,121 +3450,121 @@
         <v>0</v>
       </c>
       <c r="J8">
-        <f>$B8</f>
+        <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="K8">
-        <f t="shared" si="3"/>
+        <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="L8">
-        <f t="shared" si="3"/>
+        <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="M8">
-        <f t="shared" si="3"/>
+        <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="N8">
-        <f t="shared" si="3"/>
+        <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="O8">
-        <f t="shared" si="3"/>
+        <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="P8">
-        <f t="shared" si="3"/>
+        <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="Q8">
-        <f t="shared" si="3"/>
+        <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="R8">
-        <f t="shared" si="3"/>
+        <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="S8">
-        <f t="shared" si="3"/>
+        <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="T8">
-        <f t="shared" si="3"/>
+        <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="U8">
-        <f t="shared" si="4"/>
+        <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="V8">
-        <f t="shared" si="4"/>
+        <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="W8">
-        <f t="shared" si="4"/>
+        <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="X8">
-        <f t="shared" si="4"/>
+        <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="Y8">
-        <f t="shared" si="4"/>
+        <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="Z8">
-        <f t="shared" si="4"/>
+        <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="AA8">
-        <f t="shared" si="4"/>
+        <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="AB8">
-        <f t="shared" si="4"/>
+        <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="AC8">
-        <f t="shared" si="4"/>
+        <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="AD8">
-        <f t="shared" si="4"/>
+        <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="AE8">
-        <f t="shared" si="5"/>
+        <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="AF8">
-        <f t="shared" si="5"/>
+        <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="AG8">
-        <f t="shared" si="5"/>
+        <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="AH8">
-        <f t="shared" si="5"/>
+        <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="AI8">
-        <f t="shared" si="5"/>
+        <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="AJ8">
-        <f t="shared" si="5"/>
+        <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="AK8">
-        <f t="shared" si="5"/>
+        <f t="shared" si="1"/>
         <v>0</v>
       </c>
     </row>
     <row r="9" spans="1:37" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
-        <v>44</v>
+        <v>4</v>
       </c>
       <c r="B9">
         <v>0</v>
@@ -3589,121 +3591,121 @@
         <v>0</v>
       </c>
       <c r="J9">
-        <f>$B9</f>
+        <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="K9">
-        <f t="shared" si="3"/>
+        <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="L9">
-        <f t="shared" si="3"/>
+        <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="M9">
-        <f t="shared" si="3"/>
+        <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="N9">
-        <f t="shared" si="3"/>
+        <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="O9">
-        <f t="shared" si="3"/>
+        <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="P9">
-        <f t="shared" si="3"/>
+        <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="Q9">
-        <f t="shared" si="3"/>
+        <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="R9">
-        <f t="shared" si="3"/>
+        <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="S9">
-        <f t="shared" si="3"/>
+        <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="T9">
-        <f t="shared" si="3"/>
+        <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="U9">
-        <f t="shared" si="4"/>
+        <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="V9">
-        <f t="shared" si="4"/>
+        <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="W9">
-        <f t="shared" si="4"/>
+        <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="X9">
-        <f t="shared" si="4"/>
+        <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="Y9">
-        <f t="shared" si="4"/>
+        <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="Z9">
-        <f t="shared" si="4"/>
+        <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="AA9">
-        <f t="shared" si="4"/>
+        <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="AB9">
-        <f t="shared" si="4"/>
+        <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="AC9">
-        <f t="shared" si="4"/>
+        <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="AD9">
-        <f t="shared" si="4"/>
+        <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="AE9">
-        <f t="shared" si="5"/>
+        <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="AF9">
-        <f t="shared" si="5"/>
+        <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="AG9">
-        <f t="shared" si="5"/>
+        <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="AH9">
-        <f t="shared" si="5"/>
+        <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="AI9">
-        <f t="shared" si="5"/>
+        <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="AJ9">
-        <f t="shared" si="5"/>
+        <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="AK9">
-        <f t="shared" si="5"/>
+        <f t="shared" si="1"/>
         <v>0</v>
       </c>
     </row>
     <row r="10" spans="1:37" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
-        <v>45</v>
+        <v>5</v>
       </c>
       <c r="B10">
         <v>0</v>
@@ -3730,121 +3732,121 @@
         <v>0</v>
       </c>
       <c r="J10">
-        <f>$B10</f>
+        <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="K10">
-        <f t="shared" si="3"/>
+        <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="L10">
-        <f t="shared" si="3"/>
+        <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="M10">
-        <f t="shared" si="3"/>
+        <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="N10">
-        <f t="shared" si="3"/>
+        <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="O10">
-        <f t="shared" si="3"/>
+        <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="P10">
-        <f t="shared" si="3"/>
+        <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="Q10">
-        <f t="shared" si="3"/>
+        <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="R10">
-        <f t="shared" si="3"/>
+        <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="S10">
-        <f t="shared" si="3"/>
+        <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="T10">
-        <f t="shared" si="3"/>
+        <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="U10">
-        <f t="shared" si="4"/>
+        <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="V10">
-        <f t="shared" si="4"/>
+        <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="W10">
-        <f t="shared" si="4"/>
+        <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="X10">
-        <f t="shared" si="4"/>
+        <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="Y10">
-        <f t="shared" si="4"/>
+        <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="Z10">
-        <f t="shared" si="4"/>
+        <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="AA10">
-        <f t="shared" si="4"/>
+        <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="AB10">
-        <f t="shared" si="4"/>
+        <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="AC10">
-        <f t="shared" si="4"/>
+        <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="AD10">
-        <f t="shared" si="4"/>
+        <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="AE10">
-        <f t="shared" si="5"/>
+        <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="AF10">
-        <f t="shared" si="5"/>
+        <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="AG10">
-        <f t="shared" si="5"/>
+        <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="AH10">
-        <f t="shared" si="5"/>
+        <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="AI10">
-        <f t="shared" si="5"/>
+        <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="AJ10">
-        <f t="shared" si="5"/>
+        <f t="shared" ref="G10:AK15" si="2">$B10</f>
         <v>0</v>
       </c>
       <c r="AK10">
-        <f t="shared" si="5"/>
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
     </row>
     <row r="11" spans="1:37" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
-        <v>46</v>
+        <v>7</v>
       </c>
       <c r="B11">
         <v>0</v>
@@ -3877,262 +3879,262 @@
         <v>0</v>
       </c>
       <c r="L11">
-        <f t="shared" ref="L11:U15" si="6">$B11</f>
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="M11">
-        <f t="shared" si="6"/>
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="N11">
-        <f t="shared" si="6"/>
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="O11">
-        <f t="shared" si="6"/>
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="P11">
-        <f t="shared" si="6"/>
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="Q11">
-        <f t="shared" si="6"/>
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="R11">
-        <f t="shared" si="6"/>
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="S11">
-        <f t="shared" si="6"/>
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="T11">
-        <f t="shared" si="6"/>
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="U11">
-        <f t="shared" si="6"/>
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="V11">
-        <f t="shared" ref="V11:AE15" si="7">$B11</f>
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="W11">
-        <f t="shared" si="7"/>
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="X11">
-        <f t="shared" si="7"/>
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="Y11">
-        <f t="shared" si="7"/>
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="Z11">
-        <f t="shared" si="7"/>
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="AA11">
-        <f t="shared" si="7"/>
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="AB11">
-        <f t="shared" si="7"/>
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="AC11">
-        <f t="shared" si="7"/>
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="AD11">
-        <f t="shared" si="7"/>
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="AE11">
-        <f t="shared" si="7"/>
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="AF11">
-        <f t="shared" ref="AF11:AK15" si="8">$B11</f>
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="AG11">
-        <f t="shared" si="8"/>
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="AH11">
-        <f t="shared" si="8"/>
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="AI11">
-        <f t="shared" si="8"/>
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="AJ11">
-        <f t="shared" si="8"/>
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="AK11">
-        <f t="shared" si="8"/>
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
     </row>
     <row r="12" spans="1:37" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
-        <v>47</v>
+        <v>8</v>
       </c>
       <c r="B12">
         <f>'Wgtd Avg Expected Cap Factors'!B12</f>
         <v>5.6003999999999998E-2</v>
       </c>
       <c r="C12">
-        <f t="shared" ref="C12:K12" si="9">$B12</f>
+        <f t="shared" ref="C12:I12" si="3">$B12</f>
         <v>5.6003999999999998E-2</v>
       </c>
       <c r="D12">
-        <f t="shared" si="9"/>
+        <f t="shared" si="3"/>
         <v>5.6003999999999998E-2</v>
       </c>
       <c r="E12">
-        <f t="shared" si="9"/>
+        <f t="shared" si="3"/>
         <v>5.6003999999999998E-2</v>
       </c>
       <c r="F12">
-        <f t="shared" si="9"/>
+        <f t="shared" si="3"/>
         <v>5.6003999999999998E-2</v>
       </c>
       <c r="G12">
-        <f t="shared" si="9"/>
+        <f t="shared" si="3"/>
         <v>5.6003999999999998E-2</v>
       </c>
       <c r="H12">
-        <f t="shared" si="9"/>
+        <f t="shared" si="3"/>
         <v>5.6003999999999998E-2</v>
       </c>
       <c r="I12">
-        <f t="shared" si="9"/>
+        <f t="shared" si="3"/>
         <v>5.6003999999999998E-2</v>
       </c>
       <c r="J12">
-        <f t="shared" si="9"/>
+        <f t="shared" si="2"/>
         <v>5.6003999999999998E-2</v>
       </c>
       <c r="K12">
-        <f t="shared" si="9"/>
+        <f t="shared" si="2"/>
         <v>5.6003999999999998E-2</v>
       </c>
       <c r="L12">
-        <f t="shared" si="6"/>
+        <f t="shared" si="2"/>
         <v>5.6003999999999998E-2</v>
       </c>
       <c r="M12">
-        <f t="shared" si="6"/>
+        <f t="shared" si="2"/>
         <v>5.6003999999999998E-2</v>
       </c>
       <c r="N12">
-        <f t="shared" si="6"/>
+        <f t="shared" si="2"/>
         <v>5.6003999999999998E-2</v>
       </c>
       <c r="O12">
-        <f t="shared" si="6"/>
+        <f t="shared" si="2"/>
         <v>5.6003999999999998E-2</v>
       </c>
       <c r="P12">
-        <f t="shared" si="6"/>
+        <f t="shared" si="2"/>
         <v>5.6003999999999998E-2</v>
       </c>
       <c r="Q12">
-        <f t="shared" si="6"/>
+        <f t="shared" si="2"/>
         <v>5.6003999999999998E-2</v>
       </c>
       <c r="R12">
-        <f t="shared" si="6"/>
+        <f t="shared" si="2"/>
         <v>5.6003999999999998E-2</v>
       </c>
       <c r="S12">
-        <f t="shared" si="6"/>
+        <f t="shared" si="2"/>
         <v>5.6003999999999998E-2</v>
       </c>
       <c r="T12">
-        <f t="shared" si="6"/>
+        <f t="shared" si="2"/>
         <v>5.6003999999999998E-2</v>
       </c>
       <c r="U12">
-        <f t="shared" si="6"/>
+        <f t="shared" si="2"/>
         <v>5.6003999999999998E-2</v>
       </c>
       <c r="V12">
-        <f t="shared" si="7"/>
+        <f t="shared" si="2"/>
         <v>5.6003999999999998E-2</v>
       </c>
       <c r="W12">
-        <f t="shared" si="7"/>
+        <f t="shared" si="2"/>
         <v>5.6003999999999998E-2</v>
       </c>
       <c r="X12">
-        <f t="shared" si="7"/>
+        <f t="shared" si="2"/>
         <v>5.6003999999999998E-2</v>
       </c>
       <c r="Y12">
-        <f t="shared" si="7"/>
+        <f t="shared" si="2"/>
         <v>5.6003999999999998E-2</v>
       </c>
       <c r="Z12">
-        <f t="shared" si="7"/>
+        <f t="shared" si="2"/>
         <v>5.6003999999999998E-2</v>
       </c>
       <c r="AA12">
-        <f t="shared" si="7"/>
+        <f t="shared" si="2"/>
         <v>5.6003999999999998E-2</v>
       </c>
       <c r="AB12">
-        <f t="shared" si="7"/>
+        <f t="shared" si="2"/>
         <v>5.6003999999999998E-2</v>
       </c>
       <c r="AC12">
-        <f t="shared" si="7"/>
+        <f t="shared" si="2"/>
         <v>5.6003999999999998E-2</v>
       </c>
       <c r="AD12">
-        <f t="shared" si="7"/>
+        <f t="shared" si="2"/>
         <v>5.6003999999999998E-2</v>
       </c>
       <c r="AE12">
-        <f t="shared" si="7"/>
+        <f t="shared" si="2"/>
         <v>5.6003999999999998E-2</v>
       </c>
       <c r="AF12">
-        <f t="shared" si="8"/>
+        <f t="shared" si="2"/>
         <v>5.6003999999999998E-2</v>
       </c>
       <c r="AG12">
-        <f t="shared" si="8"/>
+        <f t="shared" si="2"/>
         <v>5.6003999999999998E-2</v>
       </c>
       <c r="AH12">
-        <f t="shared" si="8"/>
+        <f t="shared" si="2"/>
         <v>5.6003999999999998E-2</v>
       </c>
       <c r="AI12">
-        <f t="shared" si="8"/>
+        <f t="shared" si="2"/>
         <v>5.6003999999999998E-2</v>
       </c>
       <c r="AJ12">
-        <f t="shared" si="8"/>
+        <f t="shared" si="2"/>
         <v>5.6003999999999998E-2</v>
       </c>
       <c r="AK12">
-        <f t="shared" si="8"/>
+        <f t="shared" si="2"/>
         <v>5.6003999999999998E-2</v>
       </c>
     </row>
     <row r="13" spans="1:37" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
-        <v>48</v>
+        <v>9</v>
       </c>
       <c r="B13">
         <v>0</v>
@@ -4150,133 +4152,133 @@
         <v>0</v>
       </c>
       <c r="G13">
-        <f>$B13</f>
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="H13">
-        <f>$B13</f>
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="I13">
-        <f>$B13</f>
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="J13">
-        <f>$B13</f>
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="K13">
-        <f>$B13</f>
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="L13">
-        <f t="shared" si="6"/>
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="M13">
-        <f t="shared" si="6"/>
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="N13">
-        <f t="shared" si="6"/>
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="O13">
-        <f t="shared" si="6"/>
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="P13">
-        <f t="shared" si="6"/>
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="Q13">
-        <f t="shared" si="6"/>
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="R13">
-        <f t="shared" si="6"/>
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="S13">
-        <f t="shared" si="6"/>
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="T13">
-        <f t="shared" si="6"/>
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="U13">
-        <f t="shared" si="6"/>
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="V13">
-        <f t="shared" si="7"/>
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="W13">
-        <f t="shared" si="7"/>
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="X13">
-        <f t="shared" si="7"/>
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="Y13">
-        <f t="shared" si="7"/>
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="Z13">
-        <f t="shared" si="7"/>
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="AA13">
-        <f t="shared" si="7"/>
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="AB13">
-        <f t="shared" si="7"/>
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="AC13">
-        <f t="shared" si="7"/>
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="AD13">
-        <f t="shared" si="7"/>
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="AE13">
-        <f t="shared" si="7"/>
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="AF13">
-        <f t="shared" si="8"/>
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="AG13">
-        <f t="shared" si="8"/>
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="AH13">
-        <f t="shared" si="8"/>
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="AI13">
-        <f t="shared" si="8"/>
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="AJ13">
-        <f t="shared" si="8"/>
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="AK13">
-        <f t="shared" si="8"/>
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
     </row>
     <row r="14" spans="1:37" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
-        <v>49</v>
+        <v>13</v>
       </c>
       <c r="B14">
         <v>0</v>
@@ -4303,121 +4305,121 @@
         <v>0</v>
       </c>
       <c r="J14">
-        <f>$B14</f>
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="K14">
-        <f>$B14</f>
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="L14">
-        <f t="shared" si="6"/>
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="M14">
-        <f t="shared" si="6"/>
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="N14">
-        <f t="shared" si="6"/>
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="O14">
-        <f t="shared" si="6"/>
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="P14">
-        <f t="shared" si="6"/>
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="Q14">
-        <f t="shared" si="6"/>
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="R14">
-        <f t="shared" si="6"/>
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="S14">
-        <f t="shared" si="6"/>
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="T14">
-        <f t="shared" si="6"/>
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="U14">
-        <f t="shared" si="6"/>
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="V14">
-        <f t="shared" si="7"/>
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="W14">
-        <f t="shared" si="7"/>
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="X14">
-        <f t="shared" si="7"/>
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="Y14">
-        <f t="shared" si="7"/>
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="Z14">
-        <f t="shared" si="7"/>
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="AA14">
-        <f t="shared" si="7"/>
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="AB14">
-        <f t="shared" si="7"/>
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="AC14">
-        <f t="shared" si="7"/>
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="AD14">
-        <f t="shared" si="7"/>
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="AE14">
-        <f t="shared" si="7"/>
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="AF14">
-        <f t="shared" si="8"/>
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="AG14">
-        <f t="shared" si="8"/>
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="AH14">
-        <f t="shared" si="8"/>
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="AI14">
-        <f t="shared" si="8"/>
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="AJ14">
-        <f t="shared" si="8"/>
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="AK14">
-        <f t="shared" si="8"/>
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
     </row>
     <row r="15" spans="1:37" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
-        <v>50</v>
+        <v>16</v>
       </c>
       <c r="B15">
         <v>0</v>
@@ -4447,117 +4449,117 @@
         <v>0</v>
       </c>
       <c r="K15">
-        <f>$B15</f>
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="L15">
-        <f t="shared" si="6"/>
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="M15">
-        <f t="shared" si="6"/>
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="N15">
-        <f t="shared" si="6"/>
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="O15">
-        <f t="shared" si="6"/>
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="P15">
-        <f t="shared" si="6"/>
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="Q15">
-        <f t="shared" si="6"/>
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="R15">
-        <f t="shared" si="6"/>
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="S15">
-        <f t="shared" si="6"/>
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="T15">
-        <f t="shared" si="6"/>
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="U15">
-        <f t="shared" si="6"/>
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="V15">
-        <f t="shared" si="7"/>
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="W15">
-        <f t="shared" si="7"/>
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="X15">
-        <f t="shared" si="7"/>
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="Y15">
-        <f t="shared" si="7"/>
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="Z15">
-        <f t="shared" si="7"/>
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="AA15">
-        <f t="shared" si="7"/>
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="AB15">
-        <f t="shared" si="7"/>
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="AC15">
-        <f t="shared" si="7"/>
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="AD15">
-        <f t="shared" si="7"/>
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="AE15">
-        <f t="shared" si="7"/>
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="AF15">
-        <f t="shared" si="8"/>
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="AG15">
-        <f t="shared" si="8"/>
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="AH15">
-        <f t="shared" si="8"/>
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="AI15">
-        <f t="shared" si="8"/>
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="AJ15">
-        <f t="shared" si="8"/>
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="AK15">
-        <f t="shared" si="8"/>
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
     </row>
     <row r="16" spans="1:37" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
-        <v>51</v>
+        <v>17</v>
       </c>
       <c r="B16">
         <v>0</v>
@@ -4670,7 +4672,7 @@
     </row>
     <row r="17" spans="1:37" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
-        <v>52</v>
+        <v>18</v>
       </c>
       <c r="B17">
         <v>0</v>
@@ -4783,7 +4785,7 @@
     </row>
     <row r="18" spans="1:37" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
-        <v>53</v>
+        <v>19</v>
       </c>
       <c r="B18">
         <v>0</v>
@@ -4801,585 +4803,585 @@
         <v>0</v>
       </c>
       <c r="G18">
-        <f t="shared" ref="G18:AK18" si="10">F18</f>
+        <f t="shared" ref="G18:AK18" si="4">F18</f>
         <v>0</v>
       </c>
       <c r="H18">
-        <f t="shared" si="10"/>
+        <f t="shared" si="4"/>
         <v>0</v>
       </c>
       <c r="I18">
-        <f t="shared" si="10"/>
+        <f t="shared" si="4"/>
         <v>0</v>
       </c>
       <c r="J18">
-        <f t="shared" si="10"/>
+        <f t="shared" si="4"/>
         <v>0</v>
       </c>
       <c r="K18">
-        <f t="shared" si="10"/>
+        <f t="shared" si="4"/>
         <v>0</v>
       </c>
       <c r="L18">
-        <f t="shared" si="10"/>
+        <f t="shared" si="4"/>
         <v>0</v>
       </c>
       <c r="M18">
-        <f t="shared" si="10"/>
+        <f t="shared" si="4"/>
         <v>0</v>
       </c>
       <c r="N18">
-        <f t="shared" si="10"/>
+        <f t="shared" si="4"/>
         <v>0</v>
       </c>
       <c r="O18">
-        <f t="shared" si="10"/>
+        <f t="shared" si="4"/>
         <v>0</v>
       </c>
       <c r="P18">
-        <f t="shared" si="10"/>
+        <f t="shared" si="4"/>
         <v>0</v>
       </c>
       <c r="Q18">
-        <f t="shared" si="10"/>
+        <f t="shared" si="4"/>
         <v>0</v>
       </c>
       <c r="R18">
-        <f t="shared" si="10"/>
+        <f t="shared" si="4"/>
         <v>0</v>
       </c>
       <c r="S18">
-        <f t="shared" si="10"/>
+        <f t="shared" si="4"/>
         <v>0</v>
       </c>
       <c r="T18">
-        <f t="shared" si="10"/>
+        <f t="shared" si="4"/>
         <v>0</v>
       </c>
       <c r="U18">
-        <f t="shared" si="10"/>
+        <f t="shared" si="4"/>
         <v>0</v>
       </c>
       <c r="V18">
-        <f t="shared" si="10"/>
+        <f t="shared" si="4"/>
         <v>0</v>
       </c>
       <c r="W18">
-        <f t="shared" si="10"/>
+        <f t="shared" si="4"/>
         <v>0</v>
       </c>
       <c r="X18">
-        <f t="shared" si="10"/>
+        <f t="shared" si="4"/>
         <v>0</v>
       </c>
       <c r="Y18">
-        <f t="shared" si="10"/>
+        <f t="shared" si="4"/>
         <v>0</v>
       </c>
       <c r="Z18">
-        <f t="shared" si="10"/>
+        <f t="shared" si="4"/>
         <v>0</v>
       </c>
       <c r="AA18">
-        <f t="shared" si="10"/>
+        <f t="shared" si="4"/>
         <v>0</v>
       </c>
       <c r="AB18">
-        <f t="shared" si="10"/>
+        <f t="shared" si="4"/>
         <v>0</v>
       </c>
       <c r="AC18">
-        <f t="shared" si="10"/>
+        <f t="shared" si="4"/>
         <v>0</v>
       </c>
       <c r="AD18">
-        <f t="shared" si="10"/>
+        <f t="shared" si="4"/>
         <v>0</v>
       </c>
       <c r="AE18">
-        <f t="shared" si="10"/>
+        <f t="shared" si="4"/>
         <v>0</v>
       </c>
       <c r="AF18">
-        <f t="shared" si="10"/>
+        <f t="shared" si="4"/>
         <v>0</v>
       </c>
       <c r="AG18">
-        <f t="shared" si="10"/>
+        <f t="shared" si="4"/>
         <v>0</v>
       </c>
       <c r="AH18">
-        <f t="shared" si="10"/>
+        <f t="shared" si="4"/>
         <v>0</v>
       </c>
       <c r="AI18">
-        <f t="shared" si="10"/>
+        <f t="shared" si="4"/>
         <v>0</v>
       </c>
       <c r="AJ18">
-        <f t="shared" si="10"/>
+        <f t="shared" si="4"/>
         <v>0</v>
       </c>
       <c r="AK18">
-        <f t="shared" si="10"/>
+        <f t="shared" si="4"/>
         <v>0</v>
       </c>
     </row>
     <row r="19" spans="1:37" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="B19">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C19">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D19">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E19">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F19">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G19">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H19">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I19">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J19">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K19">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L19">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M19">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N19">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O19">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="P19">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q19">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R19">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S19">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T19">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="U19">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V19">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="W19">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="X19">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Y19">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Z19">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AA19">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AB19">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AC19">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AD19">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AE19">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AF19">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AG19">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AH19">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AI19">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AJ19">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AK19">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="20" spans="1:37" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="B20">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C20">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D20">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E20">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F20">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G20">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H20">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I20">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J20">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K20">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L20">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M20">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N20">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O20">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="P20">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q20">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R20">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S20">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T20">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="U20">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V20">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="W20">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="X20">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Y20">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Z20">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AA20">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AB20">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AC20">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AD20">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AE20">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AF20">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AG20">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AH20">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AI20">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AJ20">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AK20">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="21" spans="1:37" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="B21">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C21">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D21">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E21">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F21">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G21">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H21">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I21">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J21">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K21">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L21">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M21">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N21">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O21">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="P21">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q21">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R21">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S21">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T21">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="U21">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V21">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="W21">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="X21">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Y21">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Z21">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AA21">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AB21">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AC21">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AD21">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AE21">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AF21">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AG21">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AH21">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AI21">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AJ21">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AK21">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="22" spans="1:37" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="B22">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C22">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D22">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E22">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F22">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G22">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H22">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I22">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J22">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K22">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L22">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M22">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N22">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O22">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="P22">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q22">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R22">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S22">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T22">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="U22">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V22">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="W22">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="X22">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Y22">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Z22">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AA22">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AB22">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AC22">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AD22">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AE22">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AF22">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AG22">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AH22">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AI22">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AJ22">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AK22">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="23" spans="1:37" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="B23">
         <v>0</v>
@@ -5492,7 +5494,7 @@
     </row>
     <row r="24" spans="1:37" x14ac:dyDescent="0.25">
       <c r="A24" s="6" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="B24">
         <v>0</v>
@@ -5605,7 +5607,7 @@
     </row>
     <row r="25" spans="1:37" x14ac:dyDescent="0.25">
       <c r="A25" s="6" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="B25">
         <v>0</v>
@@ -5718,6 +5720,6 @@
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup orientation="portrait"/>
+  <pageSetup orientation="portrait" r:id="rId1"/>
 </worksheet>
 </file>
--- a/InputData/elec/BGDPbES/BAU Guaranteed Dispatch Perc by Elec Source.xlsx
+++ b/InputData/elec/BGDPbES/BAU Guaranteed Dispatch Perc by Elec Source.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Olivia Ashmoore\Documents\EPS_Models by Region\RMI\RMI_all_states\IA\elec\BGDPbES\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{1AB1CD2F-3030-48E6-A470-41615333E3EF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{87DE3143-D826-44CE-9E74-125353F32E2F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="13395" yWindow="345" windowWidth="15360" windowHeight="16755" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="2685" yWindow="2685" windowWidth="21600" windowHeight="12330" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="About" sheetId="1" r:id="rId1"/>
@@ -615,7 +615,7 @@
         <v>60</v>
       </c>
       <c r="C1" s="7">
-        <v>45236</v>
+        <v>45265</v>
       </c>
     </row>
     <row r="3" spans="1:3" x14ac:dyDescent="0.25">
@@ -2782,7 +2782,7 @@
         <v>0</v>
       </c>
       <c r="S3">
-        <f t="shared" ref="J3:AK10" si="1">$B3</f>
+        <f t="shared" ref="J3:AK9" si="1">$B3</f>
         <v>0</v>
       </c>
       <c r="T3">
@@ -3708,140 +3708,112 @@
         <v>5</v>
       </c>
       <c r="B10">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C10">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D10">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E10">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F10">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G10">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H10">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I10">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J10">
-        <f t="shared" si="1"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K10">
-        <f t="shared" si="1"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L10">
-        <f t="shared" si="1"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M10">
-        <f t="shared" si="1"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N10">
-        <f t="shared" si="1"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O10">
-        <f t="shared" si="1"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="P10">
-        <f t="shared" si="1"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q10">
-        <f t="shared" si="1"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R10">
-        <f t="shared" si="1"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S10">
-        <f t="shared" si="1"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T10">
-        <f t="shared" si="1"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="U10">
-        <f t="shared" si="1"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V10">
-        <f t="shared" si="1"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="W10">
-        <f t="shared" si="1"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="X10">
-        <f t="shared" si="1"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Y10">
-        <f t="shared" si="1"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Z10">
-        <f t="shared" si="1"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AA10">
-        <f t="shared" si="1"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AB10">
-        <f t="shared" si="1"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AC10">
-        <f t="shared" si="1"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AD10">
-        <f t="shared" si="1"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AE10">
-        <f t="shared" si="1"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AF10">
-        <f t="shared" si="1"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AG10">
-        <f t="shared" si="1"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AH10">
-        <f t="shared" si="1"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AI10">
-        <f t="shared" si="1"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AJ10">
-        <f t="shared" ref="G10:AK15" si="2">$B10</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AK10">
-        <f t="shared" si="2"/>
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="11" spans="1:37" x14ac:dyDescent="0.25">
@@ -3849,138 +3821,112 @@
         <v>7</v>
       </c>
       <c r="B11">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C11">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D11">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E11">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F11">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G11">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H11">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I11">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J11">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K11">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L11">
-        <f t="shared" si="2"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M11">
-        <f t="shared" si="2"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N11">
-        <f t="shared" si="2"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O11">
-        <f t="shared" si="2"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="P11">
-        <f t="shared" si="2"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q11">
-        <f t="shared" si="2"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R11">
-        <f t="shared" si="2"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S11">
-        <f t="shared" si="2"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T11">
-        <f t="shared" si="2"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="U11">
-        <f t="shared" si="2"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V11">
-        <f t="shared" si="2"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="W11">
-        <f t="shared" si="2"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="X11">
-        <f t="shared" si="2"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Y11">
-        <f t="shared" si="2"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Z11">
-        <f t="shared" si="2"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AA11">
-        <f t="shared" si="2"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AB11">
-        <f t="shared" si="2"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AC11">
-        <f t="shared" si="2"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AD11">
-        <f t="shared" si="2"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AE11">
-        <f t="shared" si="2"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AF11">
-        <f t="shared" si="2"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AG11">
-        <f t="shared" si="2"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AH11">
-        <f t="shared" si="2"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AI11">
-        <f t="shared" si="2"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AJ11">
-        <f t="shared" si="2"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AK11">
-        <f t="shared" si="2"/>
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="12" spans="1:37" x14ac:dyDescent="0.25">
@@ -3992,143 +3938,143 @@
         <v>5.6003999999999998E-2</v>
       </c>
       <c r="C12">
-        <f t="shared" ref="C12:I12" si="3">$B12</f>
+        <f t="shared" ref="C12:I12" si="2">$B12</f>
         <v>5.6003999999999998E-2</v>
       </c>
       <c r="D12">
-        <f t="shared" si="3"/>
+        <f t="shared" si="2"/>
         <v>5.6003999999999998E-2</v>
       </c>
       <c r="E12">
-        <f t="shared" si="3"/>
+        <f t="shared" si="2"/>
         <v>5.6003999999999998E-2</v>
       </c>
       <c r="F12">
-        <f t="shared" si="3"/>
+        <f t="shared" si="2"/>
         <v>5.6003999999999998E-2</v>
       </c>
       <c r="G12">
-        <f t="shared" si="3"/>
+        <f t="shared" si="2"/>
         <v>5.6003999999999998E-2</v>
       </c>
       <c r="H12">
-        <f t="shared" si="3"/>
+        <f t="shared" si="2"/>
         <v>5.6003999999999998E-2</v>
       </c>
       <c r="I12">
-        <f t="shared" si="3"/>
+        <f t="shared" si="2"/>
         <v>5.6003999999999998E-2</v>
       </c>
       <c r="J12">
-        <f t="shared" si="2"/>
+        <f t="shared" ref="G12:AK15" si="3">$B12</f>
         <v>5.6003999999999998E-2</v>
       </c>
       <c r="K12">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>5.6003999999999998E-2</v>
       </c>
       <c r="L12">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>5.6003999999999998E-2</v>
       </c>
       <c r="M12">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>5.6003999999999998E-2</v>
       </c>
       <c r="N12">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>5.6003999999999998E-2</v>
       </c>
       <c r="O12">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>5.6003999999999998E-2</v>
       </c>
       <c r="P12">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>5.6003999999999998E-2</v>
       </c>
       <c r="Q12">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>5.6003999999999998E-2</v>
       </c>
       <c r="R12">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>5.6003999999999998E-2</v>
       </c>
       <c r="S12">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>5.6003999999999998E-2</v>
       </c>
       <c r="T12">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>5.6003999999999998E-2</v>
       </c>
       <c r="U12">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>5.6003999999999998E-2</v>
       </c>
       <c r="V12">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>5.6003999999999998E-2</v>
       </c>
       <c r="W12">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>5.6003999999999998E-2</v>
       </c>
       <c r="X12">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>5.6003999999999998E-2</v>
       </c>
       <c r="Y12">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>5.6003999999999998E-2</v>
       </c>
       <c r="Z12">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>5.6003999999999998E-2</v>
       </c>
       <c r="AA12">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>5.6003999999999998E-2</v>
       </c>
       <c r="AB12">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>5.6003999999999998E-2</v>
       </c>
       <c r="AC12">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>5.6003999999999998E-2</v>
       </c>
       <c r="AD12">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>5.6003999999999998E-2</v>
       </c>
       <c r="AE12">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>5.6003999999999998E-2</v>
       </c>
       <c r="AF12">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>5.6003999999999998E-2</v>
       </c>
       <c r="AG12">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>5.6003999999999998E-2</v>
       </c>
       <c r="AH12">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>5.6003999999999998E-2</v>
       </c>
       <c r="AI12">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>5.6003999999999998E-2</v>
       </c>
       <c r="AJ12">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>5.6003999999999998E-2</v>
       </c>
       <c r="AK12">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>5.6003999999999998E-2</v>
       </c>
     </row>
@@ -4152,127 +4098,127 @@
         <v>0</v>
       </c>
       <c r="G13">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>0</v>
       </c>
       <c r="H13">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>0</v>
       </c>
       <c r="I13">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>0</v>
       </c>
       <c r="J13">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>0</v>
       </c>
       <c r="K13">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>0</v>
       </c>
       <c r="L13">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>0</v>
       </c>
       <c r="M13">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>0</v>
       </c>
       <c r="N13">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>0</v>
       </c>
       <c r="O13">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>0</v>
       </c>
       <c r="P13">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>0</v>
       </c>
       <c r="Q13">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>0</v>
       </c>
       <c r="R13">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>0</v>
       </c>
       <c r="S13">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>0</v>
       </c>
       <c r="T13">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>0</v>
       </c>
       <c r="U13">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>0</v>
       </c>
       <c r="V13">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>0</v>
       </c>
       <c r="W13">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>0</v>
       </c>
       <c r="X13">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>0</v>
       </c>
       <c r="Y13">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>0</v>
       </c>
       <c r="Z13">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>0</v>
       </c>
       <c r="AA13">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>0</v>
       </c>
       <c r="AB13">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>0</v>
       </c>
       <c r="AC13">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>0</v>
       </c>
       <c r="AD13">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>0</v>
       </c>
       <c r="AE13">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>0</v>
       </c>
       <c r="AF13">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>0</v>
       </c>
       <c r="AG13">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>0</v>
       </c>
       <c r="AH13">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>0</v>
       </c>
       <c r="AI13">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>0</v>
       </c>
       <c r="AJ13">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>0</v>
       </c>
       <c r="AK13">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>0</v>
       </c>
     </row>
@@ -4305,115 +4251,115 @@
         <v>0</v>
       </c>
       <c r="J14">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>0</v>
       </c>
       <c r="K14">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>0</v>
       </c>
       <c r="L14">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>0</v>
       </c>
       <c r="M14">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>0</v>
       </c>
       <c r="N14">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>0</v>
       </c>
       <c r="O14">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>0</v>
       </c>
       <c r="P14">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>0</v>
       </c>
       <c r="Q14">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>0</v>
       </c>
       <c r="R14">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>0</v>
       </c>
       <c r="S14">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>0</v>
       </c>
       <c r="T14">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>0</v>
       </c>
       <c r="U14">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>0</v>
       </c>
       <c r="V14">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>0</v>
       </c>
       <c r="W14">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>0</v>
       </c>
       <c r="X14">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>0</v>
       </c>
       <c r="Y14">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>0</v>
       </c>
       <c r="Z14">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>0</v>
       </c>
       <c r="AA14">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>0</v>
       </c>
       <c r="AB14">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>0</v>
       </c>
       <c r="AC14">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>0</v>
       </c>
       <c r="AD14">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>0</v>
       </c>
       <c r="AE14">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>0</v>
       </c>
       <c r="AF14">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>0</v>
       </c>
       <c r="AG14">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>0</v>
       </c>
       <c r="AH14">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>0</v>
       </c>
       <c r="AI14">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>0</v>
       </c>
       <c r="AJ14">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>0</v>
       </c>
       <c r="AK14">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>0</v>
       </c>
     </row>
@@ -4449,111 +4395,111 @@
         <v>0</v>
       </c>
       <c r="K15">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>0</v>
       </c>
       <c r="L15">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>0</v>
       </c>
       <c r="M15">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>0</v>
       </c>
       <c r="N15">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>0</v>
       </c>
       <c r="O15">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>0</v>
       </c>
       <c r="P15">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>0</v>
       </c>
       <c r="Q15">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>0</v>
       </c>
       <c r="R15">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>0</v>
       </c>
       <c r="S15">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>0</v>
       </c>
       <c r="T15">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>0</v>
       </c>
       <c r="U15">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>0</v>
       </c>
       <c r="V15">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>0</v>
       </c>
       <c r="W15">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>0</v>
       </c>
       <c r="X15">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>0</v>
       </c>
       <c r="Y15">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>0</v>
       </c>
       <c r="Z15">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>0</v>
       </c>
       <c r="AA15">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>0</v>
       </c>
       <c r="AB15">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>0</v>
       </c>
       <c r="AC15">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>0</v>
       </c>
       <c r="AD15">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>0</v>
       </c>
       <c r="AE15">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>0</v>
       </c>
       <c r="AF15">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>0</v>
       </c>
       <c r="AG15">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>0</v>
       </c>
       <c r="AH15">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>0</v>
       </c>
       <c r="AI15">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>0</v>
       </c>
       <c r="AJ15">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>0</v>
       </c>
       <c r="AK15">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>0</v>
       </c>
     </row>

--- a/InputData/elec/BGDPbES/BAU Guaranteed Dispatch Perc by Elec Source.xlsx
+++ b/InputData/elec/BGDPbES/BAU Guaranteed Dispatch Perc by Elec Source.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="26924"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="27029"/>
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Olivia Ashmoore\Documents\EPS_Models by Region\RMI\RMI_all_states\IA\elec\BGDPbES\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{87DE3143-D826-44CE-9E74-125353F32E2F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{6E336967-1C28-48ED-9EF2-B04190973482}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="2685" yWindow="2685" windowWidth="21600" windowHeight="12330" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="2730" yWindow="840" windowWidth="17430" windowHeight="17160" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="About" sheetId="1" r:id="rId1"/>
@@ -615,7 +615,7 @@
         <v>60</v>
       </c>
       <c r="C1" s="7">
-        <v>45265</v>
+        <v>45272</v>
       </c>
     </row>
     <row r="3" spans="1:3" x14ac:dyDescent="0.25">
@@ -3144,140 +3144,112 @@
         <v>2</v>
       </c>
       <c r="B6">
-        <v>0</v>
+        <v>0.35</v>
       </c>
       <c r="C6">
-        <v>0</v>
+        <v>0.35</v>
       </c>
       <c r="D6">
-        <v>0</v>
+        <v>0.35</v>
       </c>
       <c r="E6">
-        <v>0</v>
+        <v>0.35</v>
       </c>
       <c r="F6">
-        <v>0</v>
+        <v>0.35</v>
       </c>
       <c r="G6">
-        <v>0</v>
+        <v>0.35</v>
       </c>
       <c r="H6">
-        <v>0</v>
+        <v>0.35</v>
       </c>
       <c r="I6">
-        <v>0</v>
+        <v>0.35</v>
       </c>
       <c r="J6">
-        <f t="shared" si="1"/>
-        <v>0</v>
+        <v>0.35</v>
       </c>
       <c r="K6">
-        <f t="shared" si="1"/>
-        <v>0</v>
+        <v>0.35</v>
       </c>
       <c r="L6">
-        <f t="shared" si="1"/>
-        <v>0</v>
+        <v>0.35</v>
       </c>
       <c r="M6">
-        <f t="shared" si="1"/>
-        <v>0</v>
+        <v>0.35</v>
       </c>
       <c r="N6">
-        <f t="shared" si="1"/>
-        <v>0</v>
+        <v>0.35</v>
       </c>
       <c r="O6">
-        <f t="shared" si="1"/>
-        <v>0</v>
+        <v>0.35</v>
       </c>
       <c r="P6">
-        <f t="shared" si="1"/>
-        <v>0</v>
+        <v>0.35</v>
       </c>
       <c r="Q6">
-        <f t="shared" si="1"/>
-        <v>0</v>
+        <v>0.35</v>
       </c>
       <c r="R6">
-        <f t="shared" si="1"/>
-        <v>0</v>
+        <v>0.35</v>
       </c>
       <c r="S6">
-        <f t="shared" si="1"/>
-        <v>0</v>
+        <v>0.35</v>
       </c>
       <c r="T6">
-        <f t="shared" si="1"/>
-        <v>0</v>
+        <v>0.35</v>
       </c>
       <c r="U6">
-        <f t="shared" si="1"/>
-        <v>0</v>
+        <v>0.35</v>
       </c>
       <c r="V6">
-        <f t="shared" si="1"/>
-        <v>0</v>
+        <v>0.35</v>
       </c>
       <c r="W6">
-        <f t="shared" si="1"/>
-        <v>0</v>
+        <v>0.35</v>
       </c>
       <c r="X6">
-        <f t="shared" si="1"/>
-        <v>0</v>
+        <v>0.35</v>
       </c>
       <c r="Y6">
-        <f t="shared" si="1"/>
-        <v>0</v>
+        <v>0.35</v>
       </c>
       <c r="Z6">
-        <f t="shared" si="1"/>
-        <v>0</v>
+        <v>0.35</v>
       </c>
       <c r="AA6">
-        <f t="shared" si="1"/>
-        <v>0</v>
+        <v>0.35</v>
       </c>
       <c r="AB6">
-        <f t="shared" si="1"/>
-        <v>0</v>
+        <v>0.35</v>
       </c>
       <c r="AC6">
-        <f t="shared" si="1"/>
-        <v>0</v>
+        <v>0.35</v>
       </c>
       <c r="AD6">
-        <f t="shared" si="1"/>
-        <v>0</v>
+        <v>0.35</v>
       </c>
       <c r="AE6">
-        <f t="shared" si="1"/>
-        <v>0</v>
+        <v>0.35</v>
       </c>
       <c r="AF6">
-        <f t="shared" si="1"/>
-        <v>0</v>
+        <v>0.35</v>
       </c>
       <c r="AG6">
-        <f t="shared" si="1"/>
-        <v>0</v>
+        <v>0.35</v>
       </c>
       <c r="AH6">
-        <f t="shared" si="1"/>
-        <v>0</v>
+        <v>0.35</v>
       </c>
       <c r="AI6">
-        <f t="shared" si="1"/>
-        <v>0</v>
+        <v>0.35</v>
       </c>
       <c r="AJ6">
-        <f t="shared" si="1"/>
-        <v>0</v>
+        <v>0.35</v>
       </c>
       <c r="AK6">
-        <f t="shared" si="1"/>
-        <v>0</v>
+        <v>0.35</v>
       </c>
     </row>
     <row r="7" spans="1:37" x14ac:dyDescent="0.25">

--- a/InputData/elec/BGDPbES/BAU Guaranteed Dispatch Perc by Elec Source.xlsx
+++ b/InputData/elec/BGDPbES/BAU Guaranteed Dispatch Perc by Elec Source.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Olivia Ashmoore\Documents\EPS_Models by Region\RMI\RMI_all_states\IA\elec\BGDPbES\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{6E336967-1C28-48ED-9EF2-B04190973482}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{5D31AF65-E9D4-4819-B2AC-E0E9494678CE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="2730" yWindow="840" windowWidth="17430" windowHeight="17160" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="720" yWindow="660" windowWidth="16755" windowHeight="14505" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="About" sheetId="1" r:id="rId1"/>
@@ -615,7 +615,7 @@
         <v>60</v>
       </c>
       <c r="C1" s="7">
-        <v>45272</v>
+        <v>45293</v>
       </c>
     </row>
     <row r="3" spans="1:3" x14ac:dyDescent="0.25">
